--- a/Monatliches Projekt-Reporting.xlsx
+++ b/Monatliches Projekt-Reporting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aejo\switchdrive\localRepos\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA35F97-2DA6-4058-BE71-FA0685DD1D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751CBD05-40A4-4D38-99EF-2EB2DC3DD6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Id</t>
   </si>
@@ -96,6 +96,63 @@
   <si>
     <t xml:space="preserve">📝Sonstiges
 </t>
+  </si>
+  <si>
+    <t>anonymous</t>
+  </si>
+  <si>
+    <t>PA-017 (Einführung Fundraising-CRM)</t>
+  </si>
+  <si>
+    <t>Pandiani, Loris</t>
+  </si>
+  <si>
+    <t>Fertigstellung Realisierung (Realisierung)</t>
+  </si>
+  <si>
+    <t>🟢 Gut (grün)</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alle Daten sind migriert und die Funktionalitäten implementiert. Aktuell arbeiten wir am Feinschliff und gehen danach in die Optimierungsphase über. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der iterative Prozess stellt ab und zu eine Herausforderung dar, weil es nicht ganz so strukturiert verläuft. Mithilfe von Jira haben wir das aber gut in den Griff bekommen. </t>
+  </si>
+  <si>
+    <t>In der Optimierungsphase werden wir die Applikation im täglichen Alltag testen und Zusatzfunktionen, wie Dokumentengenerierung und Outlook-Anbindung ergänzen.</t>
+  </si>
+  <si>
+    <t>PA-076 (Intune Windows-Client-Integration)</t>
+  </si>
+  <si>
+    <t>Früh, Christian</t>
+  </si>
+  <si>
+    <t>12299</t>
+  </si>
+  <si>
+    <t>18800</t>
+  </si>
+  <si>
+    <t>SW Paketierung zu 80% abgeschlossen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufgrund der "fehlenden" Intune-Zertifikatprüfung auf der ISE müssen wir das Projekt auf Ende August schieben. Wir benötigen mehrere Pilotclients, um die Konfiguration und Software Pakete zu prüfen, damit wir die Phase abschliessen können. Ohne Zertifikate kann der Intune Client im Empa Netzwerk nicht aufgesetzt werden (Network Access Control NAC verhindert dies). Aktuell werden alle Intune Pilot-Clients über Eduroam aufgesetzt und betrieben. Dies ist für einen grösseren Pilot Rollout zu umständlich. </t>
+  </si>
+  <si>
+    <t>Client-Zertifikat muss gem. EuSG am 31.5.25 abgeschlossen sein. Ansonsten fällt der Projektstatus auf gelb weil sich das Projekt dann noch weiter verzögert. 
+Danach können wir hoffentlich den Pilot auf die PC Berater ausweiten und die Software Pakete testen.</t>
+  </si>
+  <si>
+    <t>Mess-Rechner werden evtl. nicht in Intune gemanagt. Mess-Rechner werden sehr wahrscheinlich in einem separatem "Projekt" verwaltet. Diese Variante werde ich noch auf Papier bringen und Fabio vorstellen. Eine Idee ist es, Mess-Clients via Microsoft Endpoint Configuration Manager (MECM) von Microsoft, ähnlich wie DSM, zu verwalten. 
+SW Pakete müssen gem. EuSG am 31.08.25 abgeschlossen sein
+DSM Wartungsvertrag gekündigt</t>
   </si>
 </sst>
 </file>
@@ -140,7 +197,16 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -200,129 +266,129 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R2" insertRow="1" totalsRowShown="0">
-  <autoFilter ref="A1:R2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R3" totalsRowShown="0">
+  <autoFilter ref="A1:R3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Startzeit">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Startzeit" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="startDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Fertigstellungszeit">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Fertigstellungszeit" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="submitDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="13">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="📂Projektname" dataDxfId="11">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="📂Projektname" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r190a7cb8938f46b1add80224517216d5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="👨‍💼Projektleiter" dataDxfId="10">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="👨‍💼Projektleiter" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r51975c76adc0402189f3761f1ac841cd"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="📊In welcher Phase befindet sich das Projekt aktuell?" dataDxfId="9">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="📊In welcher Phase befindet sich das Projekt aktuell?" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r88bc497d606043eaa8db44c1c7ef1261"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="📊Voraussichtliches Enddatum der aktuellen Phase_x000a_">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="📊Voraussichtliches Enddatum der aktuellen Phase_x000a_" dataDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8316b3fea9154d6db936ae938d59d3b0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{917EBC4F-929A-4665-B733-7F57D8987267}" name="⏳Hat sich das Enddatum - der aktuellen Phase - gegenüber dem Vormonat verändert? Falls ja, wieso?" dataDxfId="8">
+    <tableColumn id="17" xr3:uid="{917EBC4F-929A-4665-B733-7F57D8987267}" name="⏳Hat sich das Enddatum - der aktuellen Phase - gegenüber dem Vormonat verändert? Falls ja, wieso?" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r2ccfc5b86bc74c6e9173ace3bd0698f9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="✅Wie bewertest du - als Projektleiter - den aktuellen Status?_x000a_" dataDxfId="7">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="✅Wie bewertest du - als Projektleiter - den aktuellen Status?_x000a_" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r79d986dce68e4ae6bcd92dfb51552634"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="💰IST-Budget? (Bitte die bisherigen aufgelaufenen externen Kosten - gemäss Projektantrag - für das Projekt eingeben)" dataDxfId="6">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="💰IST-Budget? (Bitte die bisherigen aufgelaufenen externen Kosten - gemäss Projektantrag - für das Projekt eingeben)" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r574ccc3b83074ebfa74689b014bd45b7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="🏠IST-Budget? (Bitte die bisherigen aufgelaufenen internen Kosten - gemäss Projektantrag - für das Projekt eingeben)" dataDxfId="5">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="🏠IST-Budget? (Bitte die bisherigen aufgelaufenen internen Kosten - gemäss Projektantrag - für das Projekt eingeben)" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf2003e4878034c4c80496676d3a15e04"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="🏆Erfolge gegenüber dem letzten Monat?_x000a_" dataDxfId="4">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="🏆Erfolge gegenüber dem letzten Monat?_x000a_" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r27ef16c30d304ac599144a18d7e57225"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="⚠️Welche Herausforderungen bestehen?_x000a_" dataDxfId="3">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="⚠️Welche Herausforderungen bestehen?_x000a_" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r155936158d7e42fc9ad2ac9d3f8323f1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{0F7C008F-A098-42CE-A80D-D538D2C7B94B}" name="🚨Muss etwas an Transformation Agent eskaliert werden?" dataDxfId="2">
+    <tableColumn id="18" xr3:uid="{0F7C008F-A098-42CE-A80D-D538D2C7B94B}" name="🚨Muss etwas an Transformation Agent eskaliert werden?" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r224110003a754a8d87471691cad40b4c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="📅Ausblick auf den nächsten Monat oder wichtige anstehende Termine?_x000a_" dataDxfId="1">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="📅Ausblick auf den nächsten Monat oder wichtige anstehende Termine?_x000a_" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0aa789f4d11e4ff184cae9971acf9f2c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="📝Sonstiges_x000a_" dataDxfId="0">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="📝Sonstiges_x000a_" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6fb7c18a2a7c44879acc6e64a508dd8e"/>
@@ -655,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -727,11 +793,95 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="I2" s="2"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45782.368310185186</v>
+      </c>
+      <c r="C2" s="3">
+        <v>45782.371817129628</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2">
+        <v>45809</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45782.340185185189</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45782.399560185186</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2">
+        <v>45900</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
